--- a/output/pdf_financials_xlsx/QESS.xlsx
+++ b/output/pdf_financials_xlsx/QESS.xlsx
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.257694</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.318055</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.759544</v>
       </c>
     </row>
     <row r="93">
@@ -3448,7 +3448,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -4102,7 +4106,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>1.257694</v>
       </c>

--- a/output/pdf_financials_xlsx/QESS.xlsx
+++ b/output/pdf_financials_xlsx/QESS.xlsx
@@ -1079,16 +1079,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.5458809999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.711179</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.016093</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.006783</v>
       </c>
     </row>
     <row r="35">
@@ -1117,16 +1117,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.5458809999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.711179</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.016093</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.006783</v>
       </c>
     </row>
     <row r="37">
@@ -1345,13 +1345,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.587553</v>
+        <v>0.041672</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.818504</v>
+        <v>0.107325</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.065785</v>
+        <v>0.049692</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">

--- a/output/pdf_financials_xlsx/QESS.xlsx
+++ b/output/pdf_financials_xlsx/QESS.xlsx
@@ -547,13 +547,13 @@
         <v>0.186263</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.303888</v>
+        <v>0.459888</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.815813</v>
+        <v>1.069813</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.168198</v>
+        <v>1.419198</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>1.862736</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.250078</v>
+        <v>1.501078</v>
       </c>
     </row>
     <row r="11">
@@ -1667,10 +1667,10 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.214075</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.090311</v>
       </c>
     </row>
     <row r="65">
@@ -1727,7 +1727,7 @@
         <v>0.265615</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="68">
@@ -5680,7 +5680,11 @@
           <t>Management and director fees</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -6542,7 +6546,11 @@
           <t>Management and director fees 8</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
